--- a/Spanish La Liga/Raw/25_26.xlsx
+++ b/Spanish La Liga/Raw/25_26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP32"/>
+  <dimension ref="A1:AP42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4854,6 +4854,1366 @@
       </c>
       <c r="AP32" t="n">
         <v>81</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>7</v>
+      </c>
+      <c r="F33" t="n">
+        <v>3</v>
+      </c>
+      <c r="G33" t="n">
+        <v>53</v>
+      </c>
+      <c r="H33" t="n">
+        <v>23</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2</v>
+      </c>
+      <c r="J33" t="n">
+        <v>19</v>
+      </c>
+      <c r="K33" t="n">
+        <v>555</v>
+      </c>
+      <c r="L33" t="n">
+        <v>22</v>
+      </c>
+      <c r="M33" t="n">
+        <v>9</v>
+      </c>
+      <c r="N33" t="n">
+        <v>18</v>
+      </c>
+      <c r="O33" t="n">
+        <v>26</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>4</v>
+      </c>
+      <c r="R33" t="n">
+        <v>21</v>
+      </c>
+      <c r="S33" t="n">
+        <v>48</v>
+      </c>
+      <c r="T33" t="n">
+        <v>435</v>
+      </c>
+      <c r="U33" t="n">
+        <v>357</v>
+      </c>
+      <c r="V33" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Elche</t>
+        </is>
+      </c>
+      <c r="X33" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>47</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>505</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>13</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>57</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>384</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>309</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>80.5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" t="n">
+        <v>10</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G34" t="n">
+        <v>48</v>
+      </c>
+      <c r="H34" t="n">
+        <v>12</v>
+      </c>
+      <c r="I34" t="n">
+        <v>4</v>
+      </c>
+      <c r="J34" t="n">
+        <v>22</v>
+      </c>
+      <c r="K34" t="n">
+        <v>494</v>
+      </c>
+      <c r="L34" t="n">
+        <v>16</v>
+      </c>
+      <c r="M34" t="n">
+        <v>8</v>
+      </c>
+      <c r="N34" t="n">
+        <v>10</v>
+      </c>
+      <c r="O34" t="n">
+        <v>30</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3</v>
+      </c>
+      <c r="R34" t="n">
+        <v>24</v>
+      </c>
+      <c r="S34" t="n">
+        <v>63</v>
+      </c>
+      <c r="T34" t="n">
+        <v>390</v>
+      </c>
+      <c r="U34" t="n">
+        <v>297</v>
+      </c>
+      <c r="V34" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Oviedo</t>
+        </is>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>52</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>542</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>47</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>71</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>425</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>337</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>79.3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>22</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3</v>
+      </c>
+      <c r="G35" t="n">
+        <v>63</v>
+      </c>
+      <c r="H35" t="n">
+        <v>17</v>
+      </c>
+      <c r="I35" t="n">
+        <v>12</v>
+      </c>
+      <c r="J35" t="n">
+        <v>42</v>
+      </c>
+      <c r="K35" t="n">
+        <v>684</v>
+      </c>
+      <c r="L35" t="n">
+        <v>13</v>
+      </c>
+      <c r="M35" t="n">
+        <v>6</v>
+      </c>
+      <c r="N35" t="n">
+        <v>13</v>
+      </c>
+      <c r="O35" t="n">
+        <v>13</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>8</v>
+      </c>
+      <c r="R35" t="n">
+        <v>16</v>
+      </c>
+      <c r="S35" t="n">
+        <v>58</v>
+      </c>
+      <c r="T35" t="n">
+        <v>582</v>
+      </c>
+      <c r="U35" t="n">
+        <v>478</v>
+      </c>
+      <c r="V35" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="X35" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>37</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>470</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>37</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>11</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>79</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>337</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>253</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>75.09999999999999</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>12</v>
+      </c>
+      <c r="F36" t="n">
+        <v>3</v>
+      </c>
+      <c r="G36" t="n">
+        <v>58</v>
+      </c>
+      <c r="H36" t="n">
+        <v>17</v>
+      </c>
+      <c r="I36" t="n">
+        <v>6</v>
+      </c>
+      <c r="J36" t="n">
+        <v>35</v>
+      </c>
+      <c r="K36" t="n">
+        <v>674</v>
+      </c>
+      <c r="L36" t="n">
+        <v>20</v>
+      </c>
+      <c r="M36" t="n">
+        <v>10</v>
+      </c>
+      <c r="N36" t="n">
+        <v>16</v>
+      </c>
+      <c r="O36" t="n">
+        <v>18</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>25</v>
+      </c>
+      <c r="S36" t="n">
+        <v>59</v>
+      </c>
+      <c r="T36" t="n">
+        <v>528</v>
+      </c>
+      <c r="U36" t="n">
+        <v>406</v>
+      </c>
+      <c r="V36" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Alavés</t>
+        </is>
+      </c>
+      <c r="X36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>524</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>12</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>20</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>68</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>385</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>268</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>69.59999999999999</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" t="n">
+        <v>8</v>
+      </c>
+      <c r="F37" t="n">
+        <v>3</v>
+      </c>
+      <c r="G37" t="n">
+        <v>60</v>
+      </c>
+      <c r="H37" t="n">
+        <v>12</v>
+      </c>
+      <c r="I37" t="n">
+        <v>8</v>
+      </c>
+      <c r="J37" t="n">
+        <v>17</v>
+      </c>
+      <c r="K37" t="n">
+        <v>747</v>
+      </c>
+      <c r="L37" t="n">
+        <v>11</v>
+      </c>
+      <c r="M37" t="n">
+        <v>5</v>
+      </c>
+      <c r="N37" t="n">
+        <v>10</v>
+      </c>
+      <c r="O37" t="n">
+        <v>18</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>10</v>
+      </c>
+      <c r="R37" t="n">
+        <v>13</v>
+      </c>
+      <c r="S37" t="n">
+        <v>64</v>
+      </c>
+      <c r="T37" t="n">
+        <v>657</v>
+      </c>
+      <c r="U37" t="n">
+        <v>578</v>
+      </c>
+      <c r="V37" t="n">
+        <v>88</v>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>536</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>52</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>433</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>363</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>83.8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>20</v>
+      </c>
+      <c r="F38" t="n">
+        <v>6</v>
+      </c>
+      <c r="G38" t="n">
+        <v>59</v>
+      </c>
+      <c r="H38" t="n">
+        <v>7</v>
+      </c>
+      <c r="I38" t="n">
+        <v>10</v>
+      </c>
+      <c r="J38" t="n">
+        <v>27</v>
+      </c>
+      <c r="K38" t="n">
+        <v>787</v>
+      </c>
+      <c r="L38" t="n">
+        <v>15</v>
+      </c>
+      <c r="M38" t="n">
+        <v>8</v>
+      </c>
+      <c r="N38" t="n">
+        <v>12</v>
+      </c>
+      <c r="O38" t="n">
+        <v>12</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>4</v>
+      </c>
+      <c r="R38" t="n">
+        <v>19</v>
+      </c>
+      <c r="S38" t="n">
+        <v>55</v>
+      </c>
+      <c r="T38" t="n">
+        <v>686</v>
+      </c>
+      <c r="U38" t="n">
+        <v>596</v>
+      </c>
+      <c r="V38" t="n">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="X38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>41</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>584</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>24</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>14</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>57</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>467</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>383</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="n">
+        <v>5</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" t="n">
+        <v>33</v>
+      </c>
+      <c r="H39" t="n">
+        <v>16</v>
+      </c>
+      <c r="I39" t="n">
+        <v>4</v>
+      </c>
+      <c r="J39" t="n">
+        <v>11</v>
+      </c>
+      <c r="K39" t="n">
+        <v>436</v>
+      </c>
+      <c r="L39" t="n">
+        <v>13</v>
+      </c>
+      <c r="M39" t="n">
+        <v>9</v>
+      </c>
+      <c r="N39" t="n">
+        <v>16</v>
+      </c>
+      <c r="O39" t="n">
+        <v>40</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>12</v>
+      </c>
+      <c r="R39" t="n">
+        <v>13</v>
+      </c>
+      <c r="S39" t="n">
+        <v>58</v>
+      </c>
+      <c r="T39" t="n">
+        <v>298</v>
+      </c>
+      <c r="U39" t="n">
+        <v>212</v>
+      </c>
+      <c r="V39" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="X39" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>67</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>741</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>29</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>23</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>54</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>610</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>518</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>84.90000000000001</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" t="n">
+        <v>9</v>
+      </c>
+      <c r="F40" t="n">
+        <v>6</v>
+      </c>
+      <c r="G40" t="n">
+        <v>36</v>
+      </c>
+      <c r="H40" t="n">
+        <v>13</v>
+      </c>
+      <c r="I40" t="n">
+        <v>3</v>
+      </c>
+      <c r="J40" t="n">
+        <v>11</v>
+      </c>
+      <c r="K40" t="n">
+        <v>455</v>
+      </c>
+      <c r="L40" t="n">
+        <v>9</v>
+      </c>
+      <c r="M40" t="n">
+        <v>12</v>
+      </c>
+      <c r="N40" t="n">
+        <v>13</v>
+      </c>
+      <c r="O40" t="n">
+        <v>33</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>15</v>
+      </c>
+      <c r="R40" t="n">
+        <v>18</v>
+      </c>
+      <c r="S40" t="n">
+        <v>64</v>
+      </c>
+      <c r="T40" t="n">
+        <v>341</v>
+      </c>
+      <c r="U40" t="n">
+        <v>256</v>
+      </c>
+      <c r="V40" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>704</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>20</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>79</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>598</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>504</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>84.3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>6</v>
+      </c>
+      <c r="E41" t="n">
+        <v>24</v>
+      </c>
+      <c r="F41" t="n">
+        <v>10</v>
+      </c>
+      <c r="G41" t="n">
+        <v>71</v>
+      </c>
+      <c r="H41" t="n">
+        <v>9</v>
+      </c>
+      <c r="I41" t="n">
+        <v>5</v>
+      </c>
+      <c r="J41" t="n">
+        <v>9</v>
+      </c>
+      <c r="K41" t="n">
+        <v>832</v>
+      </c>
+      <c r="L41" t="n">
+        <v>17</v>
+      </c>
+      <c r="M41" t="n">
+        <v>8</v>
+      </c>
+      <c r="N41" t="n">
+        <v>15</v>
+      </c>
+      <c r="O41" t="n">
+        <v>23</v>
+      </c>
+      <c r="P41" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2</v>
+      </c>
+      <c r="R41" t="n">
+        <v>18</v>
+      </c>
+      <c r="S41" t="n">
+        <v>48</v>
+      </c>
+      <c r="T41" t="n">
+        <v>718</v>
+      </c>
+      <c r="U41" t="n">
+        <v>645</v>
+      </c>
+      <c r="V41" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>386</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>21</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>12</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>21</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>293</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>196</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>66.90000000000001</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" t="n">
+        <v>8</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" t="n">
+        <v>38</v>
+      </c>
+      <c r="H42" t="n">
+        <v>9</v>
+      </c>
+      <c r="I42" t="n">
+        <v>3</v>
+      </c>
+      <c r="J42" t="n">
+        <v>11</v>
+      </c>
+      <c r="K42" t="n">
+        <v>440</v>
+      </c>
+      <c r="L42" t="n">
+        <v>12</v>
+      </c>
+      <c r="M42" t="n">
+        <v>4</v>
+      </c>
+      <c r="N42" t="n">
+        <v>10</v>
+      </c>
+      <c r="O42" t="n">
+        <v>39</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R42" t="n">
+        <v>15</v>
+      </c>
+      <c r="S42" t="n">
+        <v>58</v>
+      </c>
+      <c r="T42" t="n">
+        <v>332</v>
+      </c>
+      <c r="U42" t="n">
+        <v>260</v>
+      </c>
+      <c r="V42" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="X42" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>62</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>31</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>636</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>17</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>63</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>547</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>452</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>82.59999999999999</v>
       </c>
     </row>
   </sheetData>
